--- a/InputData/elec/SoFCtMbCtPR/Shr of Fwd Costs that Must be Covered to be Prevent Retirement.xlsx
+++ b/InputData/elec/SoFCtMbCtPR/Shr of Fwd Costs that Must be Covered to be Prevent Retirement.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robbie\Models\US\Models\eps-us\InputData\elec\SoFCtMbCtPR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rachel Goldstein\Desktop\EPS Models\Mexico EPS\InputData\elec\SoFCtMbCtPR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B79CF789-70E7-4DC0-88EA-1AD99B90A68C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37AEA5B1-5524-475B-875B-890960D521EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7650" yWindow="9600" windowWidth="23010" windowHeight="13770" xr2:uid="{5E78EF81-321F-43F5-B343-4E83A6575A8A}"/>
+    <workbookView xWindow="37035" yWindow="315" windowWidth="28800" windowHeight="14115" activeTab="1" xr2:uid="{5E78EF81-321F-43F5-B343-4E83A6575A8A}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="SoFCtMbCtPR " sheetId="2" r:id="rId2"/>
+    <sheet name="SoFCtMbCtPR" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -524,14 +524,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31DA106A-E484-4E2B-B3F9-91B326CF3E2A}">
   <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -539,7 +539,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>29</v>
       </c>
@@ -547,42 +547,42 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>38</v>
       </c>
@@ -598,12 +598,12 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:B25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="34.5703125" customWidth="1"/>
+    <col min="1" max="1" width="34.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
@@ -611,7 +611,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -619,7 +619,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -627,7 +627,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -635,7 +635,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -643,7 +643,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -651,7 +651,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -659,7 +659,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -667,7 +667,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -675,7 +675,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -683,7 +683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -691,7 +691,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -699,7 +699,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -707,7 +707,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -715,7 +715,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -723,7 +723,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -731,7 +731,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -739,7 +739,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -747,7 +747,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>19</v>
       </c>
@@ -755,7 +755,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>20</v>
       </c>
@@ -763,7 +763,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>21</v>
       </c>
@@ -771,7 +771,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>22</v>
       </c>
@@ -779,7 +779,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>23</v>
       </c>
@@ -787,7 +787,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>27</v>
       </c>
@@ -795,7 +795,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>28</v>
       </c>
